--- a/Matilde360.xlsx
+++ b/Matilde360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monst\Downloads\Matilde-cotizador-main\Matilde-cotizador-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715FC893-2E32-4787-BF3B-A96414742786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD22B45-379F-4BEC-A87A-ACB922CEAF14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="102">
   <si>
     <t>Categoría</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t>Desarrollo e implementación de proyecto digital de educación médica continua</t>
+  </si>
+  <si>
+    <t>Portal de educación médica continua</t>
   </si>
 </sst>
 </file>
@@ -772,6 +775,15 @@
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -794,15 +806,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1138,14 +1141,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
     </row>
     <row r="3" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -1272,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="59" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="47" t="s">
         <v>100</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="60">
+      <c r="E9" s="48">
         <v>580000</v>
       </c>
-      <c r="F9" s="61"/>
+      <c r="F9" s="49"/>
     </row>
     <row r="10" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
     </row>
     <row r="11" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
@@ -1376,14 +1379,14 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
     </row>
     <row r="16" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
@@ -1466,14 +1469,14 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
     </row>
     <row r="21" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
@@ -1636,14 +1639,14 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="51" t="s">
+      <c r="A29" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="52"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
     </row>
     <row r="30" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
@@ -1726,14 +1729,14 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
     </row>
     <row r="35" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="32" t="s">

--- a/Matilde360.xlsx
+++ b/Matilde360.xlsx
@@ -552,16 +552,16 @@
         <v>Plataformas Digitales</v>
       </c>
       <c r="B9" t="str">
-        <v>Portal de educación médica continua</v>
+        <v>Proyecto de educación médica continua. (Desarrollo, implementación y seguimiento. Duración del proyecto 12 meses)</v>
       </c>
       <c r="C9" t="str" xml:space="preserve">
         <v xml:space="preserve">Desarrollo e implementación de proyecto digital de educación médica continua. Cobertura de 12 meses, incluyendo:
-Desarrollo Tecnológico: Diseño UX, programación de Portal Web (Back-end) y creación de App Móvil (iOS/Android) con sistema de videoconsultas médicas.
-Gestión Académica: Estructuración de agenda de temas, módulos de gamificación y trámites de aval/puntos ante CONAMEGE.
-Contenido y Media: Producción y edición audiovisual premium (Videos médicos, Reels y Podcast).
-Marketing y Comunicación: Diseño y ejecución de campañas de Email Marketing (automatización, flujos de bienvenida y fidelización).
-Analítica de Datos: Implementación de Dashboard Comercial Healthcare (KPIs) para monitoreo.
-Operación Anual: Capacitación, lanzamiento por fases, soporte técnico permanente, monitoreo de resultados y reportes mensuales durante todo el año.</v>
+• Desarrollo Tecnológico: Diseño UX, programación de Portal Web (Back-end) y creación de App Móvil (iOS/Android) con sistema de videoconsultas médicas.
+• Gestión Académica: Estructuración de agenda de temas, módulos de gamificación y trámites de aval/puntos ante CONAMEGE.
+• Contenido y Media: Producción y edición audiovisual premium (Videos médicos, Reels y Podcast).
+• Marketing y Comunicación: Diseño y ejecución de campañas de Email Marketing (automatización, flujos de bienvenida y fidelización).
+• Analítica de Datos: Implementación de Dashboard Comercial Healthcare (KPIs) para monitoreo.
+• Operación Anual: Capacitación, lanzamiento por fases, soporte técnico permanente, monitoreo de resultados y reportes mensuales durante todo el año.</v>
       </c>
       <c r="D9" t="str">
         <v>Proyecto</v>
